--- a/JUGADORES T6.xlsx
+++ b/JUGADORES T6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF323571-D91A-43AD-BC59-B6AE64B5541C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DBDC4E9-4B8F-4298-B133-E14725AF7384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{A98060DC-1932-43E6-9169-0378406E7D7E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>Rubén Serna</t>
   </si>
@@ -96,9 +96,6 @@
     <t>Alejandro Belinchón</t>
   </si>
   <si>
-    <t>Jesús Sancho</t>
-  </si>
-  <si>
     <t>Miguel Mau</t>
   </si>
   <si>
@@ -106,9 +103,6 @@
   </si>
   <si>
     <t>Jorge Alberola</t>
-  </si>
-  <si>
-    <t>Antonio Calatayud</t>
   </si>
   <si>
     <t>Álvaro Monleon</t>
@@ -511,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA3AEB69-7505-4905-87B6-66EA901D9D74}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -532,10 +526,10 @@
         <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -549,10 +543,10 @@
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -563,13 +557,13 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -580,13 +574,13 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -603,7 +597,7 @@
         <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -611,16 +605,16 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -628,16 +622,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -645,35 +639,27 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/JUGADORES T6.xlsx
+++ b/JUGADORES T6.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DBDC4E9-4B8F-4298-B133-E14725AF7384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC78DC2D-400C-472A-911D-D3142FE1ACCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{A98060DC-1932-43E6-9169-0378406E7D7E}"/>
   </bookViews>
@@ -105,9 +105,6 @@
     <t>Jorge Alberola</t>
   </si>
   <si>
-    <t>Álvaro Monleon</t>
-  </si>
-  <si>
     <t>Alex Navarro</t>
   </si>
   <si>
@@ -154,6 +151,9 @@
   </si>
   <si>
     <t>Borja Carmona</t>
+  </si>
+  <si>
+    <t>Álvaro Monleón</t>
   </si>
 </sst>
 </file>
@@ -526,10 +526,10 @@
         <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -543,10 +543,10 @@
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -560,10 +560,10 @@
         <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -574,13 +574,13 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -597,7 +597,7 @@
         <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -611,10 +611,10 @@
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -625,13 +625,13 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -645,10 +645,10 @@
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -659,7 +659,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
